--- a/OCT_2026/10-21-26/Zubaida_Traders ok.xlsx
+++ b/OCT_2026/10-21-26/Zubaida_Traders ok.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032130C4-5352-4255-A0DD-0716BF86D93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0245BEF0-D119-4EBF-AD77-0BDB7DFC96BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -47893,7 +47893,7 @@
       <c r="L4" s="372"/>
       <c r="M4" s="402">
         <f ca="1">TODAY()+1</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="N4" s="402"/>
       <c r="O4" s="402"/>
@@ -47921,7 +47921,7 @@
       <c r="L5" s="372"/>
       <c r="M5" s="402">
         <f ca="1">M4-1</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="N5" s="371"/>
       <c r="O5" s="371"/>
@@ -54116,7 +54116,7 @@
       <c r="G3" s="362"/>
       <c r="H3" s="359">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I3" s="359"/>
       <c r="J3" s="360"/>
